--- a/SGC-CKN/Excel/30f21a60-d747-42b4-821e-d6ab263ae47d_Lô_CT-02_P11-88_D800_22-03-2026.xlsx
+++ b/SGC-CKN/Excel/30f21a60-d747-42b4-821e-d6ab263ae47d_Lô_CT-02_P11-88_D800_22-03-2026.xlsx
@@ -1367,16 +1367,16 @@
         <v>-38.2</v>
       </c>
       <c r="G17" s="25">
-        <v>-45.1</v>
+        <v>-45.5</v>
       </c>
       <c r="H17" s="25">
         <v>1</v>
       </c>
       <c r="I17" s="25">
-        <v>6.9</v>
+        <v>7.3</v>
       </c>
       <c r="J17" s="12">
-        <v>6.9</v>
+        <v>7.3</v>
       </c>
       <c r="K17" s="26" t="s">
         <v>50</v>
@@ -1399,19 +1399,19 @@
         <v>53</v>
       </c>
       <c r="F18" s="28">
-        <v>-45.1</v>
+        <v>-45.5</v>
       </c>
       <c r="G18" s="28">
-        <v>-49.8</v>
+        <v>-49.81</v>
       </c>
       <c r="H18" s="28">
         <v>2.42</v>
       </c>
       <c r="I18" s="28">
-        <v>4.7</v>
+        <v>4.31</v>
       </c>
       <c r="J18" s="8">
-        <v>1.94</v>
+        <v>1.78</v>
       </c>
       <c r="K18" s="29" t="s">
         <v>54</v>
@@ -1743,16 +1743,16 @@
         <v>-38.2</v>
       </c>
       <c r="F8" s="25">
-        <v>-45.1</v>
+        <v>-45.5</v>
       </c>
       <c r="G8" s="25">
         <v>1</v>
       </c>
       <c r="H8" s="25">
-        <v>6.9</v>
+        <v>7.3</v>
       </c>
       <c r="I8" s="12">
-        <v>6.9</v>
+        <v>7.3</v>
       </c>
     </row>
     <row r="9" ht="32" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -1769,19 +1769,19 @@
         <v>1</v>
       </c>
       <c r="E9" s="28">
-        <v>-45.1</v>
+        <v>-45.5</v>
       </c>
       <c r="F9" s="28">
-        <v>-49.8</v>
+        <v>-49.81</v>
       </c>
       <c r="G9" s="28">
         <v>2.42</v>
       </c>
       <c r="H9" s="28">
-        <v>4.7</v>
+        <v>4.31</v>
       </c>
       <c r="I9" s="8">
-        <v>1.94</v>
+        <v>1.78</v>
       </c>
     </row>
     <row r="10" ht="28" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -1801,13 +1801,13 @@
         <v>-1.6</v>
       </c>
       <c r="F10" s="33">
-        <v>-49.8</v>
+        <v>-49.81</v>
       </c>
       <c r="G10" s="33">
         <v>8.42</v>
       </c>
       <c r="H10" s="33">
-        <v>48.2</v>
+        <v>48.21</v>
       </c>
       <c r="I10" s="33">
         <v>5.73</v>
